--- a/artfynd/A 17101-2023 artfynd.xlsx
+++ b/artfynd/A 17101-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123666896</v>
+        <v>123666878</v>
       </c>
       <c r="B2" t="n">
-        <v>57632</v>
+        <v>57493</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103020</v>
+        <v>100048</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,12 +708,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -761,6 +769,11 @@
           <t>2025-03-30</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Två mindre hackspettar födosöker på klibbalarna runt bäcken. Rikligt med klibbalar med hack.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -769,6 +782,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Bäckravin</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -785,10 +803,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123666878</v>
+        <v>123666896</v>
       </c>
       <c r="B3" t="n">
-        <v>57487</v>
+        <v>57638</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,16 +819,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100048</v>
+        <v>103020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -818,20 +836,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -879,11 +889,6 @@
           <t>2025-03-30</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Två mindre hackspettar födosöker på klibbalarna runt bäcken. Rikligt med klibbalar med hack.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -892,11 +897,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Bäckravin</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">

--- a/artfynd/A 17101-2023 artfynd.xlsx
+++ b/artfynd/A 17101-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123666878</v>
       </c>
       <c r="B2" t="n">
-        <v>57493</v>
+        <v>57496</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>123666896</v>
       </c>
       <c r="B3" t="n">
-        <v>57638</v>
+        <v>57641</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 17101-2023 artfynd.xlsx
+++ b/artfynd/A 17101-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123666878</v>
+        <v>123666896</v>
       </c>
       <c r="B2" t="n">
-        <v>57496</v>
+        <v>57642</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100048</v>
+        <v>103020</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,20 +708,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -769,11 +761,6 @@
           <t>2025-03-30</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Två mindre hackspettar födosöker på klibbalarna runt bäcken. Rikligt med klibbalar med hack.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -782,11 +769,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Bäckravin</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -803,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123666896</v>
+        <v>123666878</v>
       </c>
       <c r="B3" t="n">
-        <v>57641</v>
+        <v>57497</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,16 +801,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -836,12 +818,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -889,6 +879,11 @@
           <t>2025-03-30</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Två mindre hackspettar födosöker på klibbalarna runt bäcken. Rikligt med klibbalar med hack.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -897,6 +892,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Bäckravin</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">

--- a/artfynd/A 17101-2023 artfynd.xlsx
+++ b/artfynd/A 17101-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123666896</v>
+        <v>123666878</v>
       </c>
       <c r="B2" t="n">
-        <v>57642</v>
+        <v>57497</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103020</v>
+        <v>100048</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,12 +708,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -761,6 +769,11 @@
           <t>2025-03-30</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Två mindre hackspettar födosöker på klibbalarna runt bäcken. Rikligt med klibbalar med hack.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -769,6 +782,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Bäckravin</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -785,10 +803,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123666878</v>
+        <v>123666896</v>
       </c>
       <c r="B3" t="n">
-        <v>57497</v>
+        <v>57642</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,16 +819,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100048</v>
+        <v>103020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -818,20 +836,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -879,11 +889,6 @@
           <t>2025-03-30</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Två mindre hackspettar födosöker på klibbalarna runt bäcken. Rikligt med klibbalar med hack.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -892,11 +897,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Bäckravin</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">

--- a/artfynd/A 17101-2023 artfynd.xlsx
+++ b/artfynd/A 17101-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123666878</v>
+        <v>123666896</v>
       </c>
       <c r="B2" t="n">
-        <v>57497</v>
+        <v>57642</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100048</v>
+        <v>103020</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,20 +708,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -769,11 +761,6 @@
           <t>2025-03-30</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Två mindre hackspettar födosöker på klibbalarna runt bäcken. Rikligt med klibbalar med hack.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -782,11 +769,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Bäckravin</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -803,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123666896</v>
+        <v>123666878</v>
       </c>
       <c r="B3" t="n">
-        <v>57642</v>
+        <v>57497</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,16 +801,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -836,12 +818,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -889,6 +879,11 @@
           <t>2025-03-30</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Två mindre hackspettar födosöker på klibbalarna runt bäcken. Rikligt med klibbalar med hack.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -897,6 +892,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Bäckravin</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">

--- a/artfynd/A 17101-2023 artfynd.xlsx
+++ b/artfynd/A 17101-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,58 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123666896</v>
+        <v>75801373</v>
       </c>
       <c r="B2" t="n">
-        <v>57664</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103020</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Pinglaström, Upl</t>
+          <t>Lunsen SO, vid Pinglaström, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>654452</v>
+        <v>654511</v>
       </c>
       <c r="R2" t="n">
-        <v>6629119</v>
+        <v>6628983</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,12 +749,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2001-10-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2001-10-30</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>1 kapsel på murken granved.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,31 +770,36 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Murken granved. # Gran</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123666878</v>
+        <v>114802431</v>
       </c>
       <c r="B3" t="n">
-        <v>57519</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,53 +807,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100048</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Pinglaström, Upl</t>
+          <t>finnvreten, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>654452</v>
+        <v>654495</v>
       </c>
       <c r="R3" t="n">
-        <v>6629119</v>
+        <v>6628954</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,17 +864,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2024-01-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Två mindre hackspettar födosöker på klibbalarna runt bäcken. Rikligt med klibbalar med hack.</t>
+          <t>2024-01-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,26 +878,371 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Bäckravin</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Carin von Köhler</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Carin von Köhler</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123666826</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Pinglaström, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>654471</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6629167</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Björn Bråvander</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Björn Bråvander</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123666878</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57966</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Pinglaström, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>654452</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6629119</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Två mindre hackspettar födosöker på klibbalarna runt bäcken. Rikligt med klibbalar med hack.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Bäckravin</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123666896</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Pinglaström, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>654452</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6629119</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17101-2023 artfynd.xlsx
+++ b/artfynd/A 17101-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75801373</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114802431</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1015,6 +1030,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123666826</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1138,6 +1158,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123666878</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1243,8 +1268,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123666896</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>